--- a/code/experiment/1024chunk_Qwen3_5topk_Y.xlsx
+++ b/code/experiment/1024chunk_Qwen3_5topk_Y.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5017B4-C296-4663-86DB-19ECCE9D9DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34955491-3FB7-4433-B3D2-4F389C2365E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -207,9 +207,6 @@
     <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
   </si>
   <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
-  </si>
-  <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
   </si>
   <si>
@@ -614,6 +611,10 @@
     <t>MAIN-RAG 采用了一种训练无关的多智能体过滤方法，通过多个LLM智能体协作对检索文档进行过滤和评分，并引入自适应阈值机制动态调整相关性阈值，以提升检索精度和系统可靠性。RAG-Critic 则采用了一种批评者引导的智能体工作流，通过构建层次化错误体系并训练错误批评模型，自动提供细粒度错误反馈，进而驱动基于错误的自我修正过程。
 来自: [MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation, 第1页, MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation_chunk_001]
 来自: [RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation, 第1页, RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation_chunk_000]</t>
+  </si>
+  <si>
+    <t>CypherBench 提出了什么核心方法来应对 RDF 查询的挑战？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1052,7 +1053,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -1097,7 +1098,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -1131,7 +1132,7 @@
       </c>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="252" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1142,7 +1143,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1176,7 +1177,7 @@
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="336" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -1187,7 +1188,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1232,7 +1233,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1277,7 +1278,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1311,7 +1312,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="154" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1367,7 +1368,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1401,7 +1402,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="406" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -1412,7 +1413,7 @@
         <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1457,7 +1458,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1491,7 +1492,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="154" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="196" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -1502,7 +1503,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1536,7 +1537,7 @@
       </c>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="308" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="280" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -1547,7 +1548,7 @@
         <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1581,7 +1582,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="350" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -1592,7 +1593,7 @@
         <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1637,7 +1638,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1671,7 +1672,7 @@
       </c>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="392" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -1682,7 +1683,7 @@
         <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -1716,7 +1717,7 @@
       </c>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="336" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
@@ -1727,7 +1728,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1761,7 +1762,7 @@
       </c>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="336" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1817,7 +1818,7 @@
         <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -1851,7 +1852,7 @@
       </c>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="227" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>53</v>
       </c>
@@ -1862,7 +1863,7 @@
         <v>54</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -1896,18 +1897,18 @@
       </c>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" ht="266" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="294" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1943,16 +1944,16 @@
     </row>
     <row r="22" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -1988,16 +1989,16 @@
     </row>
     <row r="23" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2031,18 +2032,18 @@
       </c>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="196" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2076,18 +2077,18 @@
       </c>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" ht="308" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="392" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2121,63 +2122,63 @@
       </c>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="196" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2">
-        <v>1</v>
-      </c>
-      <c r="M26" s="2">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" ht="392" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2213,16 +2214,16 @@
     </row>
     <row r="28" spans="1:15" ht="182" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -2256,18 +2257,18 @@
       </c>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" ht="168" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="336" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -2303,16 +2304,16 @@
     </row>
     <row r="30" spans="1:15" ht="406" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2348,16 +2349,16 @@
     </row>
     <row r="31" spans="1:15" ht="322" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
@@ -2393,16 +2394,16 @@
     </row>
     <row r="32" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2438,16 +2439,16 @@
     </row>
     <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2483,16 +2484,16 @@
     </row>
     <row r="34" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2526,18 +2527,18 @@
       </c>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="308" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="350" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
@@ -2571,18 +2572,18 @@
       </c>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" ht="406" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
@@ -2616,18 +2617,18 @@
       </c>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="392" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -2663,16 +2664,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -2708,16 +2709,16 @@
     </row>
     <row r="39" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
@@ -2753,16 +2754,16 @@
     </row>
     <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2798,16 +2799,16 @@
     </row>
     <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2843,16 +2844,16 @@
     </row>
     <row r="42" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E42" s="2">
         <v>1</v>
@@ -2888,16 +2889,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -2933,16 +2934,16 @@
     </row>
     <row r="44" spans="1:15" ht="112" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -2970,16 +2971,16 @@
     </row>
     <row r="45" spans="1:15" ht="140" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -3007,16 +3008,16 @@
     </row>
     <row r="46" spans="1:15" ht="84" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -3044,16 +3045,16 @@
     </row>
     <row r="47" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -3081,16 +3082,16 @@
     </row>
     <row r="48" spans="1:15" ht="98" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -3118,16 +3119,16 @@
     </row>
     <row r="49" spans="1:15" ht="98" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -3155,16 +3156,16 @@
     </row>
     <row r="50" spans="1:15" ht="126" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -3192,16 +3193,16 @@
     </row>
     <row r="51" spans="1:15" ht="126" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -3229,7 +3230,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E53">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3270,7 +3271,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B54" t="s">
         <v>16</v>
@@ -3314,7 +3315,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
         <v>41</v>
@@ -3358,10 +3359,10 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E56">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3402,10 +3403,10 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E57">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3446,10 +3447,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E58" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>
